--- a/jogos_2026-07-09.xlsx
+++ b/jogos_2026-07-09.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N2" t="n">

--- a/jogos_2026-07-09.xlsx
+++ b/jogos_2026-07-09.xlsx
@@ -731,28 +731,28 @@
         <v>3.75</v>
       </c>
       <c r="P2" t="n">
-        <v>3.9</v>
+        <v>4.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>2.31</v>
+        <v>2.63</v>
       </c>
       <c r="S2" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="T2" t="n">
-        <v>3.34</v>
+        <v>4.5</v>
       </c>
       <c r="U2" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="W2" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -761,28 +761,28 @@
         <v>1.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.17</v>
+        <v>1.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>

--- a/jogos_2026-07-09.xlsx
+++ b/jogos_2026-07-09.xlsx
@@ -728,19 +728,19 @@
         <v>1.64</v>
       </c>
       <c r="O2" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P2" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R2" t="n">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="S2" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T2" t="n">
         <v>4.5</v>
@@ -749,7 +749,7 @@
         <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="W2" t="n">
         <v>1.2</v>
@@ -758,31 +758,31 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z2" t="n">
         <v>6.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>

--- a/jogos_2026-07-09.xlsx
+++ b/jogos_2026-07-09.xlsx
@@ -731,16 +731,16 @@
         <v>3.9</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q2" t="n">
         <v>2.1</v>
       </c>
       <c r="R2" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T2" t="n">
         <v>4.5</v>
@@ -758,10 +758,10 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA2" t="n">
         <v>1.4</v>
@@ -770,19 +770,19 @@
         <v>2.75</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AK2" t="n">
         <v>2.07</v>

--- a/jogos_2026-07-09.xlsx
+++ b/jogos_2026-07-09.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="O2" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P2" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="S2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.17</v>
-      </c>
-      <c r="T2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.2</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z2" t="n">
         <v>6</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
